--- a/data/source/xlsx/FocalizingAgents.xlsx
+++ b/data/source/xlsx/FocalizingAgents.xlsx
@@ -1708,7 +1708,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Voce narrante gaddiana: onnisciente ma pervasa di digressioni, ironia e plurilinguismo; focalizzatore a pieno titolo.</t>
+          <t>Focalizzatore quando il luogo non appartiene a un personaggio o gruppo riconoscibile, oppure, come in QP 61, quando rappresenta l'autore.</t>
         </is>
       </c>
     </row>
